--- a/lojas-proprias/pwr_reports/Keys Summary - Lojas Corporativas (Stores)(2026-08-31 - 2026-09-06).xlsx
+++ b/lojas-proprias/pwr_reports/Keys Summary - Lojas Corporativas (Stores)(2026-08-31 - 2026-09-06).xlsx
@@ -204,36 +204,36 @@
   </si>
   <si>
     <t>22
-21</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>R$ 1.188.954,81</t>
-  </si>
-  <si>
-    <t>R$ 58.200,59
-R$ 56.616,90</t>
+20</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>R$ 1.203.716,31</t>
+  </si>
+  <si>
+    <t>R$ 58.513,99
+R$ 57.536,14</t>
   </si>
   <si>
     <t>9.9%
-9.5%</t>
-  </si>
-  <si>
-    <t>639.6</t>
-  </si>
-  <si>
-    <t>4.2%</t>
-  </si>
-  <si>
-    <t>31.0%</t>
-  </si>
-  <si>
-    <t>(6.0%)</t>
-  </si>
-  <si>
-    <t>3.3%</t>
+5.1%</t>
+  </si>
+  <si>
+    <t>642.5</t>
+  </si>
+  <si>
+    <t>4.3%</t>
+  </si>
+  <si>
+    <t>31.3%</t>
+  </si>
+  <si>
+    <t>(5.7%)</t>
+  </si>
+  <si>
+    <t>3.2%</t>
   </si>
   <si>
     <t>0.5%</t>
@@ -242,7 +242,7 @@
     <t>24.9</t>
   </si>
   <si>
-    <t>77.4%</t>
+    <t>76.8%</t>
   </si>
   <si>
     <t>5.5%</t>
@@ -254,13 +254,13 @@
     <t>4.0</t>
   </si>
   <si>
-    <t>10.5</t>
-  </si>
-  <si>
-    <t>17.8</t>
-  </si>
-  <si>
-    <t>81.4%</t>
+    <t>11.3</t>
+  </si>
+  <si>
+    <t>17.9</t>
+  </si>
+  <si>
+    <t>81.0%</t>
   </si>
   <si>
     <t>-R$ 10.967,30</t>
@@ -915,7 +915,7 @@
         <v>62936.809999999998</v>
       </c>
       <c r="Q2" s="6">
-        <v>-0.04141016412608689</v>
+        <v>-0.086655717782919139</v>
       </c>
       <c r="R2" s="7">
         <v>624</v>
@@ -951,7 +951,7 @@
         <v>5.1121146236559136</v>
       </c>
       <c r="AC2" s="8">
-        <v>9.7551330000000007</v>
+        <v>11.747479999999999</v>
       </c>
       <c r="AD2" s="8">
         <v>18.605060297239913</v>
@@ -1046,7 +1046,7 @@
         <v>58306.690000000002</v>
       </c>
       <c r="Q3" s="6">
-        <v>0.31435284453733781</v>
+        <v>0.25231539004933734</v>
       </c>
       <c r="R3" s="7">
         <v>615</v>
@@ -1082,7 +1082,7 @@
         <v>4.195184198645598</v>
       </c>
       <c r="AC3" s="8">
-        <v>11.404849</v>
+        <v>12.085146</v>
       </c>
       <c r="AD3" s="8">
         <v>17.312687612612613</v>
@@ -1177,7 +1177,7 @@
         <v>72495.698333333334</v>
       </c>
       <c r="Q4" s="6">
-        <v>0.067361552906411548</v>
+        <v>0.11350043230699614</v>
       </c>
       <c r="R4" s="7">
         <v>742</v>
@@ -1213,7 +1213,7 @@
         <v>2.4556716075156575</v>
       </c>
       <c r="AC4" s="8">
-        <v>10.286336</v>
+        <v>10.279680000000001</v>
       </c>
       <c r="AD4" s="8">
         <v>17.127641308793457</v>
@@ -1308,7 +1308,7 @@
         <v>57792.499999999993</v>
       </c>
       <c r="Q5" s="6">
-        <v>0.016742181592607652</v>
+        <v>-0.038263604220407532</v>
       </c>
       <c r="R5" s="7">
         <v>627</v>
@@ -1344,7 +1344,7 @@
         <v>4.1882147757255934</v>
       </c>
       <c r="AC5" s="8">
-        <v>9.5175599999999996</v>
+        <v>9.9315040000000003</v>
       </c>
       <c r="AD5" s="8">
         <v>16.834385789473686</v>
@@ -1441,7 +1441,7 @@
         <v>56422.489999999998</v>
       </c>
       <c r="Q6" s="6">
-        <v>0.062290956597671032</v>
+        <v>0.01215065346492028</v>
       </c>
       <c r="R6" s="7">
         <v>651</v>
@@ -1477,7 +1477,7 @@
         <v>4.215543789473684</v>
       </c>
       <c r="AC6" s="8">
-        <v>16.356766</v>
+        <v>15.55817</v>
       </c>
       <c r="AD6" s="8">
         <v>22.495017473684211</v>
@@ -1572,7 +1572,7 @@
         <v>63132.999999999993</v>
       </c>
       <c r="Q7" s="6">
-        <v>0.034651220455129694</v>
+        <v>-0.014184420419357191</v>
       </c>
       <c r="R7" s="7">
         <v>645</v>
@@ -1608,7 +1608,7 @@
         <v>4.5093905376344079</v>
       </c>
       <c r="AC7" s="8">
-        <v>10.91391</v>
+        <v>10.957877999999999</v>
       </c>
       <c r="AD7" s="8">
         <v>16.949645319148935</v>
@@ -1701,7 +1701,7 @@
         <v>59028.350000000013</v>
       </c>
       <c r="Q8" s="6">
-        <v>0.48736822955145387</v>
+        <v>0.41716427657059252</v>
       </c>
       <c r="R8" s="7">
         <v>543</v>
@@ -1737,7 +1737,7 @@
         <v>3.041359736842105</v>
       </c>
       <c r="AC8" s="8">
-        <v>9.5348009999999999</v>
+        <v>9.4425830000000008</v>
       </c>
       <c r="AD8" s="8">
         <v>16.358005249343829</v>
@@ -1832,7 +1832,7 @@
         <v>53864.37000000001</v>
       </c>
       <c r="Q9" s="6">
-        <v>-0.26484213267472023</v>
+        <v>-0.14115416390519486</v>
       </c>
       <c r="R9" s="7">
         <v>541.80000000000007</v>
@@ -1963,7 +1963,7 @@
         <v>91425.589999999997</v>
       </c>
       <c r="Q10" s="6">
-        <v>0.094779185331478555</v>
+        <v>0.036073248234408828</v>
       </c>
       <c r="R10" s="7">
         <v>1010.9999999999999</v>
@@ -1999,7 +1999,7 @@
         <v>4.6731739197530864</v>
       </c>
       <c r="AC10" s="8">
-        <v>11.363913999999999</v>
+        <v>12.477563</v>
       </c>
       <c r="AD10" s="8">
         <v>19.322036474164133</v>
@@ -2094,7 +2094,7 @@
         <v>132844.76000000001</v>
       </c>
       <c r="Q11" s="6">
-        <v>0.17825852109197005</v>
+        <v>0.12314680864501204</v>
       </c>
       <c r="R11" s="7">
         <v>1477</v>
@@ -2130,7 +2130,7 @@
         <v>4.0861827956989245</v>
       </c>
       <c r="AC11" s="8">
-        <v>9.9802700000000009</v>
+        <v>14.550172</v>
       </c>
       <c r="AD11" s="8">
         <v>21.336505362776023</v>
@@ -2225,7 +2225,7 @@
         <v>37969.699999999997</v>
       </c>
       <c r="Q12" s="6">
-        <v>0.32268649957326723</v>
+        <v>0.26025563111690975</v>
       </c>
       <c r="R12" s="7">
         <v>397</v>
@@ -2261,7 +2261,7 @@
         <v>4.4368600682593859</v>
       </c>
       <c r="AC12" s="8">
-        <v>9.3405889999999996</v>
+        <v>9.6093449999999994</v>
       </c>
       <c r="AD12" s="8">
         <v>15.493107457627119</v>
@@ -2356,7 +2356,7 @@
         <v>82645.729999999996</v>
       </c>
       <c r="Q13" s="6">
-        <v>0.04028208016816559</v>
+        <v>-0.0088192658551238257</v>
       </c>
       <c r="R13" s="7">
         <v>1043</v>
@@ -2392,7 +2392,7 @@
         <v>2.1588602011494253</v>
       </c>
       <c r="AC13" s="8">
-        <v>12.905319</v>
+        <v>12.712719</v>
       </c>
       <c r="AD13" s="8">
         <v>18.048155216284989</v>
@@ -2489,7 +2489,7 @@
         <v>36440.470000000001</v>
       </c>
       <c r="Q14" s="6">
-        <v>0.14176968258334899</v>
+        <v>0.087878166381714529</v>
       </c>
       <c r="R14" s="7">
         <v>374</v>
@@ -2525,7 +2525,7 @@
         <v>7.0677484732824425</v>
       </c>
       <c r="AC14" s="8">
-        <v>11.925347</v>
+        <v>12.353367</v>
       </c>
       <c r="AD14" s="8">
         <v>18.902503296703294</v>
@@ -2717,7 +2717,7 @@
         <v>34879</v>
       </c>
       <c r="Q16" s="6">
-        <v>-0.049861111754301524</v>
+        <v>-0.094707755862052267</v>
       </c>
       <c r="R16" s="7">
         <v>384</v>
@@ -2753,7 +2753,7 @@
         <v>5.6260504201680677</v>
       </c>
       <c r="AC16" s="8">
-        <v>12.421106999999999</v>
+        <v>11.997807</v>
       </c>
       <c r="AD16" s="8">
         <v>18.352642276422763</v>
@@ -2848,7 +2848,7 @@
         <v>42400.909999999996</v>
       </c>
       <c r="Q17" s="6">
-        <v>0.17161400457638076</v>
+        <v>0.11631370585291245</v>
       </c>
       <c r="R17" s="7">
         <v>492.00000000000006</v>
@@ -2884,7 +2884,7 @@
         <v>3.9142569277108437</v>
       </c>
       <c r="AC17" s="8">
-        <v>12.540797</v>
+        <v>13.590633</v>
       </c>
       <c r="AD17" s="8">
         <v>20.361094925373134</v>
@@ -2977,7 +2977,7 @@
         <v>59246.400000000001</v>
       </c>
       <c r="Q18" s="6">
-        <v>0.022707205733722535</v>
+        <v>-0.025564651751828871</v>
       </c>
       <c r="R18" s="7">
         <v>757</v>
@@ -3013,7 +3013,7 @@
         <v>2.4355480408858603</v>
       </c>
       <c r="AC18" s="8">
-        <v>4.2414880000000004</v>
+        <v>4.2595989999999997</v>
       </c>
       <c r="AD18" s="8">
         <v>11.189049405772495</v>
@@ -3065,7 +3065,7 @@
         <v>19714</v>
       </c>
       <c r="B19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C19" s="4">
         <v>44</v>
@@ -3102,55 +3102,55 @@
         <v>52</v>
       </c>
       <c r="O19" s="5">
-        <v>47387.619999999995</v>
+        <v>62149.119999999995</v>
       </c>
       <c r="P19" s="5">
-        <v>55285.556666666664</v>
+        <v>62149.119999999995</v>
       </c>
       <c r="Q19" s="6">
-        <v>0.054496957785768574</v>
+        <v>0.12945869902688867</v>
       </c>
       <c r="R19" s="7">
-        <v>572.83333333333326</v>
+        <v>641</v>
       </c>
       <c r="S19" s="6">
-        <v>0.11590909090909096</v>
+        <v>0.11478260869565227</v>
       </c>
       <c r="T19" s="6">
-        <v>0.30081856822520309</v>
+        <v>0.36030144755066523</v>
       </c>
       <c r="U19" s="6">
-        <v>0.0042345659056099456</v>
+        <v>0.064801527358714001</v>
       </c>
       <c r="V19" s="6">
-        <v>0.021562403851470069</v>
+        <v>0.019827312116406474</v>
       </c>
       <c r="W19" s="6">
-        <v>-0.0072267609135044132</v>
+        <v>-0.0070250391316884295</v>
       </c>
       <c r="X19" s="8">
-        <v>24.077483565459609</v>
+        <v>25.306796311475409</v>
       </c>
       <c r="Y19" s="6">
-        <v>0.75623268698060941</v>
+        <v>0.65714285714285714</v>
       </c>
       <c r="Z19" s="6">
-        <v>0.058495821727019497</v>
+        <v>0.065573770491803282</v>
       </c>
       <c r="AA19" s="8">
-        <v>6.5235311475409841</v>
+        <v>6.8271351562499998</v>
       </c>
       <c r="AB19" s="8">
-        <v>3.7139904225352112</v>
+        <v>4.3805206249999999</v>
       </c>
       <c r="AC19" s="8">
         <v>10.413611</v>
       </c>
       <c r="AD19" s="8">
-        <v>17.297539275766017</v>
+        <v>18.238592827868853</v>
       </c>
       <c r="AE19" s="6">
-        <v>0.81894150417827294</v>
+        <v>0.75409836065573765</v>
       </c>
       <c r="AF19" s="9"/>
       <c r="AG19" s="5">
@@ -3239,7 +3239,7 @@
         <v>35609.209999999999</v>
       </c>
       <c r="Q20" s="6">
-        <v>0.025640427431665502</v>
+        <v>-0.022769884508103022</v>
       </c>
       <c r="R20" s="7">
         <v>465</v>
@@ -3248,10 +3248,10 @@
         <v>-0.041237113402061931</v>
       </c>
       <c r="T20" s="6">
-        <v>0.36043323623298579</v>
+        <v>0.35617526476998507</v>
       </c>
       <c r="U20" s="6">
-        <v>0.026628863712505838</v>
+        <v>0.022370892249505114</v>
       </c>
       <c r="V20" s="6">
         <v>0.041109196188289489</v>
@@ -3275,7 +3275,7 @@
         <v>4.2015841628959274</v>
       </c>
       <c r="AC20" s="8">
-        <v>6.740685</v>
+        <v>6.9194560000000003</v>
       </c>
       <c r="AD20" s="8">
         <v>13.867345248868778</v>
@@ -3370,7 +3370,7 @@
         <v>26435.409999999996</v>
       </c>
       <c r="Q21" s="6">
-        <v>0.10861815102889993</v>
+        <v>0.056291238572671931</v>
       </c>
       <c r="R21" s="7">
         <v>333</v>
@@ -3379,10 +3379,10 @@
         <v>0.1404109589041096</v>
       </c>
       <c r="T21" s="6">
-        <v>0.37661637175288754</v>
+        <v>0.36005712413766233</v>
       </c>
       <c r="U21" s="6">
-        <v>0.051045858566218572</v>
+        <v>0.034486610950993382</v>
       </c>
       <c r="V21" s="6">
         <v>0.11300509430343618</v>
@@ -3406,7 +3406,7 @@
         <v>1.838024120603015</v>
       </c>
       <c r="AC21" s="8">
-        <v>5.9628019999999999</v>
+        <v>5.9415480000000001</v>
       </c>
       <c r="AD21" s="8">
         <v>13.645753365384614</v>
@@ -3502,9 +3502,7 @@
       <c r="P22" s="5">
         <v>52993.590000000004</v>
       </c>
-      <c r="Q22" s="6">
-        <v>0.12103644528384261</v>
-      </c>
+      <c r="Q22" s="6"/>
       <c r="R22" s="7">
         <v>527</v>
       </c>
@@ -3512,10 +3510,10 @@
         <v>0.09563409563409575</v>
       </c>
       <c r="T22" s="6">
-        <v>0.31703813612174608</v>
+        <v>0.31683263957018198</v>
       </c>
       <c r="U22" s="6">
-        <v>-0.015447358822076407</v>
+        <v>-0.015652855373640473</v>
       </c>
       <c r="V22" s="6">
         <v>0.02053705929339756</v>
@@ -3539,7 +3537,7 @@
         <v>4.581191588785047</v>
       </c>
       <c r="AC22" s="8">
-        <v>9.5925460000000005</v>
+        <v>9.8049280000000003</v>
       </c>
       <c r="AD22" s="8">
         <v>15.858119580419581</v>
@@ -3634,7 +3632,7 @@
         <v>50442.860000000001</v>
       </c>
       <c r="Q23" s="6">
-        <v>0.050877153509363948</v>
+        <v>0.0012757403492238417</v>
       </c>
       <c r="R23" s="7">
         <v>588</v>
@@ -3670,7 +3668,7 @@
         <v>4.171243896713615</v>
       </c>
       <c r="AC23" s="8">
-        <v>12.160764</v>
+        <v>12.496418999999999</v>
       </c>
       <c r="AD23" s="8">
         <v>19.280665197215779</v>
